--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ186"/>
+  <dimension ref="A1:AZ188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10643,48 +10643,52 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135323088</v>
+        <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>97386</v>
+        <v>83343</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2869</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>628090</v>
+        <v>628151</v>
       </c>
       <c r="R85" t="n">
-        <v>7301469</v>
+        <v>7301498</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10708,22 +10712,27 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10738,31 +10747,27 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135323088</t>
+          <t>https://artportalen.se/Sighting/137007767</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>96001582</v>
+        <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>89156</v>
+        <v>83343</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10770,37 +10775,41 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4412</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>628074</v>
+        <v>628237</v>
       </c>
       <c r="R86" t="n">
-        <v>7301340</v>
+        <v>7301372</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10824,12 +10833,27 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10844,65 +10868,65 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001582</t>
+          <t>https://artportalen.se/Sighting/137007768</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135321659</v>
+        <v>135323088</v>
       </c>
       <c r="B87" t="n">
-        <v>79441</v>
+        <v>97386</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>628029</v>
+        <v>628090</v>
       </c>
       <c r="R87" t="n">
-        <v>7301453</v>
+        <v>7301469</v>
       </c>
       <c r="S87" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10931,7 +10955,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10941,7 +10965,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10956,12 +10980,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
@@ -10971,54 +10995,54 @@
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321659</t>
+          <t>https://artportalen.se/Sighting/135323088</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135321666</v>
+        <v>96001582</v>
       </c>
       <c r="B88" t="n">
-        <v>79441</v>
+        <v>89156</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>627995</v>
+        <v>628074</v>
       </c>
       <c r="R88" t="n">
-        <v>7301349</v>
+        <v>7301340</v>
       </c>
       <c r="S88" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11042,22 +11066,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:09</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11072,28 +11086,24 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321666</t>
+          <t>https://artportalen.se/Sighting/96001582</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135323658</v>
+        <v>135321659</v>
       </c>
       <c r="B89" t="n">
         <v>79441</v>
@@ -11124,17 +11134,17 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>628066</v>
+        <v>628029</v>
       </c>
       <c r="R89" t="n">
-        <v>7301429</v>
+        <v>7301453</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11163,7 +11173,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11173,7 +11183,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11188,12 +11198,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Jennica Andersson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
@@ -11203,13 +11213,13 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135323658</t>
+          <t>https://artportalen.se/Sighting/135321659</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135379339</v>
+        <v>135321666</v>
       </c>
       <c r="B90" t="n">
         <v>79441</v>
@@ -11240,17 +11250,17 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>628090</v>
+        <v>627995</v>
       </c>
       <c r="R90" t="n">
-        <v>7301465</v>
+        <v>7301349</v>
       </c>
       <c r="S90" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11279,7 +11289,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11289,7 +11299,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11304,12 +11314,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
@@ -11319,13 +11329,13 @@
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135379339</t>
+          <t>https://artportalen.se/Sighting/135321666</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135379340</v>
+        <v>135323658</v>
       </c>
       <c r="B91" t="n">
         <v>79441</v>
@@ -11356,17 +11366,17 @@
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>628031</v>
+        <v>628066</v>
       </c>
       <c r="R91" t="n">
-        <v>7301352</v>
+        <v>7301429</v>
       </c>
       <c r="S91" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11395,7 +11405,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11405,7 +11415,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11420,12 +11430,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Jennica Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
@@ -11435,54 +11445,54 @@
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135379340</t>
+          <t>https://artportalen.se/Sighting/135323658</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135321660</v>
+        <v>135379339</v>
       </c>
       <c r="B92" t="n">
-        <v>78844</v>
+        <v>79441</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>628083</v>
+        <v>628090</v>
       </c>
       <c r="R92" t="n">
-        <v>7301469</v>
+        <v>7301465</v>
       </c>
       <c r="S92" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11511,7 +11521,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11521,7 +11531,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11536,12 +11546,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
@@ -11551,54 +11561,54 @@
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321660</t>
+          <t>https://artportalen.se/Sighting/135379339</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135321668</v>
+        <v>135379340</v>
       </c>
       <c r="B93" t="n">
-        <v>78844</v>
+        <v>79441</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>627946</v>
+        <v>628031</v>
       </c>
       <c r="R93" t="n">
-        <v>7301332</v>
+        <v>7301352</v>
       </c>
       <c r="S93" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11627,7 +11637,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11637,7 +11647,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11652,12 +11662,12 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
@@ -11667,16 +11677,16 @@
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321668</t>
+          <t>https://artportalen.se/Sighting/135379340</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>96001584</v>
+        <v>135321660</v>
       </c>
       <c r="B94" t="n">
-        <v>83307</v>
+        <v>78844</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11684,37 +11694,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>628280</v>
+        <v>628083</v>
       </c>
       <c r="R94" t="n">
-        <v>7301383</v>
+        <v>7301469</v>
       </c>
       <c r="S94" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -11738,12 +11748,22 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11758,27 +11778,31 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001584</t>
+          <t>https://artportalen.se/Sighting/135321660</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135321663</v>
+        <v>135321668</v>
       </c>
       <c r="B95" t="n">
-        <v>83428</v>
+        <v>78844</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11786,21 +11810,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11810,10 +11834,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>628017</v>
+        <v>627946</v>
       </c>
       <c r="R95" t="n">
-        <v>7301363</v>
+        <v>7301332</v>
       </c>
       <c r="S95" t="n">
         <v>4</v>
@@ -11845,7 +11869,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11855,7 +11879,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11885,16 +11909,16 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321663</t>
+          <t>https://artportalen.se/Sighting/135321668</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135321665</v>
+        <v>96001584</v>
       </c>
       <c r="B96" t="n">
-        <v>83428</v>
+        <v>83307</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11922,17 +11946,17 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>627995</v>
+        <v>628280</v>
       </c>
       <c r="R96" t="n">
-        <v>7301345</v>
+        <v>7301383</v>
       </c>
       <c r="S96" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11956,22 +11980,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>14:06</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11986,31 +12000,27 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321665</t>
+          <t>https://artportalen.se/Sighting/96001584</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135325374</v>
+        <v>135321663</v>
       </c>
       <c r="B97" t="n">
-        <v>80060</v>
+        <v>83428</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12018,37 +12028,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>628254</v>
+        <v>628017</v>
       </c>
       <c r="R97" t="n">
-        <v>7301530</v>
+        <v>7301363</v>
       </c>
       <c r="S97" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -12077,7 +12087,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -12087,7 +12097,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -12102,12 +12112,12 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
@@ -12117,54 +12127,54 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325374</t>
+          <t>https://artportalen.se/Sighting/135321663</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135325376</v>
+        <v>135321665</v>
       </c>
       <c r="B98" t="n">
-        <v>80560</v>
+        <v>83428</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>628295</v>
+        <v>627995</v>
       </c>
       <c r="R98" t="n">
-        <v>7301544</v>
+        <v>7301345</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -12193,7 +12203,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -12203,7 +12213,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -12218,12 +12228,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
@@ -12233,16 +12243,16 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325376</t>
+          <t>https://artportalen.se/Sighting/135321665</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135321671</v>
+        <v>135325374</v>
       </c>
       <c r="B99" t="n">
-        <v>57980</v>
+        <v>80060</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12250,42 +12260,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>627959</v>
+        <v>628254</v>
       </c>
       <c r="R99" t="n">
-        <v>7301383</v>
+        <v>7301530</v>
       </c>
       <c r="S99" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12314,7 +12319,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12324,19 +12329,14 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:33</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>skalad klen gran</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="b">
         <v>0</v>
@@ -12344,12 +12344,12 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
@@ -12359,59 +12359,54 @@
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321671</t>
+          <t>https://artportalen.se/Sighting/135325374</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135321672</v>
+        <v>135325376</v>
       </c>
       <c r="B100" t="n">
-        <v>57980</v>
+        <v>80560</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>627992</v>
+        <v>628295</v>
       </c>
       <c r="R100" t="n">
-        <v>7301405</v>
+        <v>7301544</v>
       </c>
       <c r="S100" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -12440,7 +12435,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12450,19 +12445,14 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>skalad klen gran</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="b">
         <v>0</v>
@@ -12470,12 +12460,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
@@ -12485,13 +12475,13 @@
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321672</t>
+          <t>https://artportalen.se/Sighting/135325376</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135323090</v>
+        <v>135321671</v>
       </c>
       <c r="B101" t="n">
         <v>57980</v>
@@ -12520,27 +12510,24 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
       <c r="M101" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>628037</v>
+        <v>627959</v>
       </c>
       <c r="R101" t="n">
-        <v>7301362</v>
+        <v>7301383</v>
       </c>
       <c r="S101" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12569,7 +12556,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12579,19 +12566,19 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>skalad klen gran</t>
         </is>
       </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG101" t="b">
         <v>0</v>
@@ -12599,12 +12586,12 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
@@ -12614,13 +12601,13 @@
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135323090</t>
+          <t>https://artportalen.se/Sighting/135321671</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135323092</v>
+        <v>135321672</v>
       </c>
       <c r="B102" t="n">
         <v>57980</v>
@@ -12649,27 +12636,24 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
       <c r="M102" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>628020</v>
+        <v>627992</v>
       </c>
       <c r="R102" t="n">
-        <v>7301366</v>
+        <v>7301405</v>
       </c>
       <c r="S102" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12698,7 +12682,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12708,7 +12692,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>skalad klen gran</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12723,12 +12712,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
@@ -12738,13 +12727,13 @@
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135323092</t>
+          <t>https://artportalen.se/Sighting/135321672</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135325377</v>
+        <v>135323090</v>
       </c>
       <c r="B103" t="n">
         <v>57980</v>
@@ -12773,19 +12762,27 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>628250</v>
+        <v>628037</v>
       </c>
       <c r="R103" t="n">
-        <v>7301387</v>
+        <v>7301362</v>
       </c>
       <c r="S103" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -12814,7 +12811,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12824,12 +12821,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12844,12 +12841,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
@@ -12859,13 +12856,13 @@
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325377</t>
+          <t>https://artportalen.se/Sighting/135323090</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135325378</v>
+        <v>135323092</v>
       </c>
       <c r="B104" t="n">
         <v>57980</v>
@@ -12898,23 +12895,23 @@
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>628206</v>
+        <v>628020</v>
       </c>
       <c r="R104" t="n">
-        <v>7301387</v>
+        <v>7301366</v>
       </c>
       <c r="S104" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12943,7 +12940,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:07</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12953,12 +12950,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre barksprätt</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12973,12 +12965,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
@@ -12988,13 +12980,13 @@
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325378</t>
+          <t>https://artportalen.se/Sighting/135323092</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135326036</v>
+        <v>135325377</v>
       </c>
       <c r="B105" t="n">
         <v>57980</v>
@@ -13023,23 +13015,19 @@
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>628266</v>
+        <v>628250</v>
       </c>
       <c r="R105" t="n">
-        <v>7301577</v>
+        <v>7301387</v>
       </c>
       <c r="S105" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -13068,7 +13056,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -13078,12 +13066,12 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>Ringhack, äldre spår</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -13098,12 +13086,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
@@ -13113,59 +13101,62 @@
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135326036</t>
+          <t>https://artportalen.se/Sighting/135325377</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135321667</v>
+        <v>135325378</v>
       </c>
       <c r="B106" t="n">
-        <v>99193</v>
+        <v>57980</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>627989</v>
+        <v>628206</v>
       </c>
       <c r="R106" t="n">
-        <v>7301335</v>
+        <v>7301387</v>
       </c>
       <c r="S106" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -13194,7 +13185,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -13204,14 +13195,19 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Äldre barksprätt</t>
         </is>
       </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
       <c r="AE106" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG106" t="b">
         <v>0</v>
@@ -13219,12 +13215,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
@@ -13234,59 +13230,58 @@
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321667</t>
+          <t>https://artportalen.se/Sighting/135325378</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135321669</v>
+        <v>135326036</v>
       </c>
       <c r="B107" t="n">
-        <v>99193</v>
+        <v>57980</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>627932</v>
+        <v>628266</v>
       </c>
       <c r="R107" t="n">
-        <v>7301350</v>
+        <v>7301577</v>
       </c>
       <c r="S107" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -13315,7 +13310,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -13325,7 +13320,12 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre spår</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -13340,12 +13340,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
@@ -13355,16 +13355,16 @@
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321669</t>
+          <t>https://artportalen.se/Sighting/135326036</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135321658</v>
+        <v>135321667</v>
       </c>
       <c r="B108" t="n">
-        <v>107784</v>
+        <v>99193</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13372,37 +13372,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221705</v>
+        <v>219790</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ängskovall</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Melampyrum pratense</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>627771</v>
+        <v>627989</v>
       </c>
       <c r="R108" t="n">
-        <v>7301879</v>
+        <v>7301335</v>
       </c>
       <c r="S108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -13431,7 +13436,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13441,7 +13446,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13471,16 +13476,16 @@
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321658</t>
+          <t>https://artportalen.se/Sighting/135321667</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>96001585</v>
+        <v>135321669</v>
       </c>
       <c r="B109" t="n">
-        <v>97983</v>
+        <v>99193</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13488,37 +13493,42 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>628237</v>
+        <v>627932</v>
       </c>
       <c r="R109" t="n">
-        <v>7301396</v>
+        <v>7301350</v>
       </c>
       <c r="S109" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -13542,12 +13552,22 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13562,27 +13582,31 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
-        </is>
-      </c>
-      <c r="AY109" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001585</t>
+          <t>https://artportalen.se/Sighting/135321669</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135323095</v>
+        <v>135321658</v>
       </c>
       <c r="B110" t="n">
-        <v>98138</v>
+        <v>107784</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13590,16 +13614,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221945</v>
+        <v>221705</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ängskovall</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Melampyrum pratense</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -13610,17 +13634,17 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>627986</v>
+        <v>627771</v>
       </c>
       <c r="R110" t="n">
-        <v>7301352</v>
+        <v>7301879</v>
       </c>
       <c r="S110" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -13649,7 +13673,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13659,7 +13683,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13674,12 +13698,12 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -13689,16 +13713,16 @@
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135323095</t>
+          <t>https://artportalen.se/Sighting/135321658</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135321662</v>
+        <v>96001585</v>
       </c>
       <c r="B111" t="n">
-        <v>99298</v>
+        <v>97983</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13706,42 +13730,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>628131</v>
+        <v>628237</v>
       </c>
       <c r="R111" t="n">
-        <v>7301366</v>
+        <v>7301396</v>
       </c>
       <c r="S111" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -13765,22 +13784,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13795,31 +13804,27 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY111" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321662</t>
+          <t>https://artportalen.se/Sighting/96001585</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135321664</v>
+        <v>135323095</v>
       </c>
       <c r="B112" t="n">
-        <v>99298</v>
+        <v>98138</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13827,42 +13832,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>628007</v>
+        <v>627986</v>
       </c>
       <c r="R112" t="n">
-        <v>7301339</v>
+        <v>7301352</v>
       </c>
       <c r="S112" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13916,12 +13916,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
@@ -13931,13 +13931,13 @@
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321664</t>
+          <t>https://artportalen.se/Sighting/135323095</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135321670</v>
+        <v>135321662</v>
       </c>
       <c r="B113" t="n">
         <v>99298</v>
@@ -13968,7 +13968,7 @@
       <c r="I113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
@@ -13977,10 +13977,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>627925</v>
+        <v>628131</v>
       </c>
       <c r="R113" t="n">
-        <v>7301347</v>
+        <v>7301366</v>
       </c>
       <c r="S113" t="n">
         <v>4</v>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -14022,7 +14022,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -14052,13 +14052,13 @@
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321670</t>
+          <t>https://artportalen.se/Sighting/135321662</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135323089</v>
+        <v>135321664</v>
       </c>
       <c r="B114" t="n">
         <v>99298</v>
@@ -14087,19 +14087,24 @@
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>628067</v>
+        <v>628007</v>
       </c>
       <c r="R114" t="n">
-        <v>7301423</v>
+        <v>7301339</v>
       </c>
       <c r="S114" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -14128,7 +14133,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -14138,7 +14143,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -14153,12 +14158,12 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
@@ -14168,13 +14173,13 @@
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135323089</t>
+          <t>https://artportalen.se/Sighting/135321664</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135323093</v>
+        <v>135321670</v>
       </c>
       <c r="B115" t="n">
         <v>99298</v>
@@ -14203,19 +14208,24 @@
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>628002</v>
+        <v>627925</v>
       </c>
       <c r="R115" t="n">
-        <v>7301358</v>
+        <v>7301347</v>
       </c>
       <c r="S115" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -14244,7 +14254,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -14254,7 +14264,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -14269,12 +14279,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
@@ -14284,16 +14294,16 @@
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135323093</t>
+          <t>https://artportalen.se/Sighting/135321670</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>96001579</v>
+        <v>135323089</v>
       </c>
       <c r="B116" t="n">
-        <v>92333</v>
+        <v>99298</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14301,37 +14311,37 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4217</v>
+        <v>221952</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>628617</v>
+        <v>628067</v>
       </c>
       <c r="R116" t="n">
-        <v>7301277</v>
+        <v>7301423</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -14355,17 +14365,22 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14380,65 +14395,69 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
-        </is>
-      </c>
-      <c r="AY116" t="inlineStr"/>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001579</t>
+          <t>https://artportalen.se/Sighting/135323089</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135325384</v>
+        <v>135323093</v>
       </c>
       <c r="B117" t="n">
-        <v>92296</v>
+        <v>99298</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>65</v>
+        <v>221952</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Maskaure Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>628596</v>
+        <v>628002</v>
       </c>
       <c r="R117" t="n">
-        <v>7301997</v>
+        <v>7301358</v>
       </c>
       <c r="S117" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -14467,7 +14486,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14477,7 +14496,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>16:03</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14492,12 +14511,12 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
@@ -14507,38 +14526,38 @@
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325384</t>
+          <t>https://artportalen.se/Sighting/135323093</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>96001591</v>
+        <v>96001579</v>
       </c>
       <c r="B118" t="n">
-        <v>78993</v>
+        <v>92333</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>4217</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14548,10 +14567,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>628910</v>
+        <v>628617</v>
       </c>
       <c r="R118" t="n">
-        <v>7301638</v>
+        <v>7301277</v>
       </c>
       <c r="S118" t="n">
         <v>25</v>
@@ -14586,6 +14605,11 @@
           <t>2021-09-09</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -14609,54 +14633,54 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001591</t>
+          <t>https://artportalen.se/Sighting/96001579</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>95999776</v>
+        <v>135325384</v>
       </c>
       <c r="B119" t="n">
-        <v>79406</v>
+        <v>92296</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>864</v>
+        <v>65</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>628854</v>
+        <v>628596</v>
       </c>
       <c r="R119" t="n">
-        <v>7301765</v>
+        <v>7301997</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -14680,12 +14704,22 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14700,27 +14734,31 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Maj Aspebo, Isak Vahlström, Björn Mildh, Kristina Bäck</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95999776</t>
+          <t>https://artportalen.se/Sighting/135325384</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>96001561</v>
+        <v>96001591</v>
       </c>
       <c r="B120" t="n">
-        <v>79406</v>
+        <v>78993</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14728,21 +14766,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14752,10 +14790,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>629029</v>
+        <v>628910</v>
       </c>
       <c r="R120" t="n">
-        <v>7301888</v>
+        <v>7301638</v>
       </c>
       <c r="S120" t="n">
         <v>25</v>
@@ -14813,16 +14851,16 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001561</t>
+          <t>https://artportalen.se/Sighting/96001591</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>96001574</v>
+        <v>95999776</v>
       </c>
       <c r="B121" t="n">
-        <v>91909</v>
+        <v>79406</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14830,21 +14868,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14854,13 +14892,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>628490</v>
+        <v>628854</v>
       </c>
       <c r="R121" t="n">
-        <v>7301367</v>
+        <v>7301765</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14904,27 +14942,27 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Maj Aspebo, Isak Vahlström, Björn Mildh, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001574</t>
+          <t>https://artportalen.se/Sighting/95999776</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>96001575</v>
+        <v>96001561</v>
       </c>
       <c r="B122" t="n">
-        <v>91909</v>
+        <v>79406</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14932,21 +14970,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14956,10 +14994,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>628438</v>
+        <v>629029</v>
       </c>
       <c r="R122" t="n">
-        <v>7301363</v>
+        <v>7301888</v>
       </c>
       <c r="S122" t="n">
         <v>25</v>
@@ -15017,13 +15055,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001575</t>
+          <t>https://artportalen.se/Sighting/96001561</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>96001590</v>
+        <v>96001574</v>
       </c>
       <c r="B123" t="n">
         <v>91909</v>
@@ -15058,10 +15096,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>628946</v>
+        <v>628490</v>
       </c>
       <c r="R123" t="n">
-        <v>7301557</v>
+        <v>7301367</v>
       </c>
       <c r="S123" t="n">
         <v>25</v>
@@ -15119,13 +15157,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001590</t>
+          <t>https://artportalen.se/Sighting/96001574</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>96001603</v>
+        <v>96001575</v>
       </c>
       <c r="B124" t="n">
         <v>91909</v>
@@ -15160,10 +15198,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>628854</v>
+        <v>628438</v>
       </c>
       <c r="R124" t="n">
-        <v>7301478</v>
+        <v>7301363</v>
       </c>
       <c r="S124" t="n">
         <v>25</v>
@@ -15221,16 +15259,16 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001603</t>
+          <t>https://artportalen.se/Sighting/96001575</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>96001592</v>
+        <v>96001590</v>
       </c>
       <c r="B125" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15238,21 +15276,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15262,10 +15300,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>628944</v>
+        <v>628946</v>
       </c>
       <c r="R125" t="n">
-        <v>7301551</v>
+        <v>7301557</v>
       </c>
       <c r="S125" t="n">
         <v>25</v>
@@ -15323,16 +15361,16 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001592</t>
+          <t>https://artportalen.se/Sighting/96001590</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>96001600</v>
+        <v>96001603</v>
       </c>
       <c r="B126" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15340,21 +15378,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -15364,10 +15402,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>628859</v>
+        <v>628854</v>
       </c>
       <c r="R126" t="n">
-        <v>7301431</v>
+        <v>7301478</v>
       </c>
       <c r="S126" t="n">
         <v>25</v>
@@ -15425,16 +15463,16 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001600</t>
+          <t>https://artportalen.se/Sighting/96001603</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>96001526</v>
+        <v>96001592</v>
       </c>
       <c r="B127" t="n">
-        <v>83173</v>
+        <v>92369</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15442,37 +15480,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1312</v>
+        <v>1209</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>628801</v>
+        <v>628944</v>
       </c>
       <c r="R127" t="n">
-        <v>7301715</v>
+        <v>7301551</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -15516,49 +15554,49 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001526</t>
+          <t>https://artportalen.se/Sighting/96001592</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>96001577</v>
+        <v>96001600</v>
       </c>
       <c r="B128" t="n">
-        <v>92292</v>
+        <v>92369</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1506</v>
+        <v>1209</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15568,10 +15606,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>628491</v>
+        <v>628859</v>
       </c>
       <c r="R128" t="n">
-        <v>7301366</v>
+        <v>7301431</v>
       </c>
       <c r="S128" t="n">
         <v>25</v>
@@ -15629,54 +15667,54 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001577</t>
+          <t>https://artportalen.se/Sighting/96001600</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>96001589</v>
+        <v>96001526</v>
       </c>
       <c r="B129" t="n">
-        <v>92292</v>
+        <v>83173</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>628943</v>
+        <v>628801</v>
       </c>
       <c r="R129" t="n">
-        <v>7301551</v>
+        <v>7301715</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -15720,24 +15758,24 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001589</t>
+          <t>https://artportalen.se/Sighting/96001526</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>96001601</v>
+        <v>96001577</v>
       </c>
       <c r="B130" t="n">
         <v>92292</v>
@@ -15772,10 +15810,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>628863</v>
+        <v>628491</v>
       </c>
       <c r="R130" t="n">
-        <v>7301428</v>
+        <v>7301366</v>
       </c>
       <c r="S130" t="n">
         <v>25</v>
@@ -15833,16 +15871,16 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001601</t>
+          <t>https://artportalen.se/Sighting/96001577</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>96001520</v>
+        <v>96001589</v>
       </c>
       <c r="B131" t="n">
-        <v>92283</v>
+        <v>92292</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15850,37 +15888,37 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2063</v>
+        <v>1506</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>628681</v>
+        <v>628943</v>
       </c>
       <c r="R131" t="n">
-        <v>7301561</v>
+        <v>7301551</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15924,65 +15962,65 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001520</t>
+          <t>https://artportalen.se/Sighting/96001589</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135325383</v>
+        <v>96001601</v>
       </c>
       <c r="B132" t="n">
-        <v>92103</v>
+        <v>92292</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2079</v>
+        <v>1506</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>628596</v>
+        <v>628863</v>
       </c>
       <c r="R132" t="n">
-        <v>7301997</v>
+        <v>7301428</v>
       </c>
       <c r="S132" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -16006,22 +16044,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -16036,53 +16064,49 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325383</t>
+          <t>https://artportalen.se/Sighting/96001601</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>96001527</v>
+        <v>96001520</v>
       </c>
       <c r="B133" t="n">
-        <v>92333</v>
+        <v>92283</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4217</v>
+        <v>2063</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -16092,10 +16116,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>628812</v>
+        <v>628681</v>
       </c>
       <c r="R133" t="n">
-        <v>7301699</v>
+        <v>7301561</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -16153,54 +16177,54 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001527</t>
+          <t>https://artportalen.se/Sighting/96001520</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>91822633</v>
+        <v>135325383</v>
       </c>
       <c r="B134" t="n">
-        <v>79327</v>
+        <v>92103</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Rutsabäcken, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>628874</v>
+        <v>628596</v>
       </c>
       <c r="R134" t="n">
-        <v>7301963</v>
+        <v>7301997</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -16224,12 +16248,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16244,65 +16278,69 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY134" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91822633</t>
+          <t>https://artportalen.se/Sighting/135325383</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>95999780</v>
+        <v>96001527</v>
       </c>
       <c r="B135" t="n">
-        <v>79327</v>
+        <v>92333</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>628884</v>
+        <v>628812</v>
       </c>
       <c r="R135" t="n">
-        <v>7301763</v>
+        <v>7301699</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -16351,19 +16389,19 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95999780</t>
+          <t>https://artportalen.se/Sighting/96001527</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>95999781</v>
+        <v>91822633</v>
       </c>
       <c r="B136" t="n">
         <v>79327</v>
@@ -16394,14 +16432,14 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>Rutsabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>628680</v>
+        <v>628874</v>
       </c>
       <c r="R136" t="n">
-        <v>7301953</v>
+        <v>7301963</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -16428,12 +16466,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -16448,24 +16486,24 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95999781</t>
+          <t>https://artportalen.se/Sighting/91822633</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>96001524</v>
+        <v>95999780</v>
       </c>
       <c r="B137" t="n">
         <v>79327</v>
@@ -16496,17 +16534,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>628859</v>
+        <v>628884</v>
       </c>
       <c r="R137" t="n">
-        <v>7301978</v>
+        <v>7301763</v>
       </c>
       <c r="S137" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -16555,19 +16593,19 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001524</t>
+          <t>https://artportalen.se/Sighting/95999780</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>96001525</v>
+        <v>95999781</v>
       </c>
       <c r="B138" t="n">
         <v>79327</v>
@@ -16598,17 +16636,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>628802</v>
+        <v>628680</v>
       </c>
       <c r="R138" t="n">
-        <v>7301709</v>
+        <v>7301953</v>
       </c>
       <c r="S138" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -16657,19 +16695,19 @@
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001525</t>
+          <t>https://artportalen.se/Sighting/95999781</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>96001594</v>
+        <v>96001524</v>
       </c>
       <c r="B139" t="n">
         <v>79327</v>
@@ -16700,17 +16738,17 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>628933</v>
+        <v>628859</v>
       </c>
       <c r="R139" t="n">
-        <v>7301670</v>
+        <v>7301978</v>
       </c>
       <c r="S139" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -16754,24 +16792,24 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001594</t>
+          <t>https://artportalen.se/Sighting/96001524</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>96001595</v>
+        <v>96001525</v>
       </c>
       <c r="B140" t="n">
         <v>79327</v>
@@ -16802,17 +16840,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>628817</v>
+        <v>628802</v>
       </c>
       <c r="R140" t="n">
-        <v>7301410</v>
+        <v>7301709</v>
       </c>
       <c r="S140" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16856,24 +16894,24 @@
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001595</t>
+          <t>https://artportalen.se/Sighting/96001525</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>96001596</v>
+        <v>96001594</v>
       </c>
       <c r="B141" t="n">
         <v>79327</v>
@@ -16908,10 +16946,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>628763</v>
+        <v>628933</v>
       </c>
       <c r="R141" t="n">
-        <v>7301364</v>
+        <v>7301670</v>
       </c>
       <c r="S141" t="n">
         <v>25</v>
@@ -16969,54 +17007,54 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001596</t>
+          <t>https://artportalen.se/Sighting/96001594</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>96001528</v>
+        <v>96001595</v>
       </c>
       <c r="B142" t="n">
-        <v>78730</v>
+        <v>79327</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>628527</v>
+        <v>628817</v>
       </c>
       <c r="R142" t="n">
-        <v>7301837</v>
+        <v>7301410</v>
       </c>
       <c r="S142" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -17060,65 +17098,65 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001528</t>
+          <t>https://artportalen.se/Sighting/96001595</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>96001510</v>
+        <v>96001596</v>
       </c>
       <c r="B143" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>628617</v>
+        <v>628763</v>
       </c>
       <c r="R143" t="n">
-        <v>7301892</v>
+        <v>7301364</v>
       </c>
       <c r="S143" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -17162,27 +17200,27 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001510</t>
+          <t>https://artportalen.se/Sighting/96001596</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>96001511</v>
+        <v>96001528</v>
       </c>
       <c r="B144" t="n">
-        <v>83307</v>
+        <v>78730</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17190,21 +17228,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -17214,10 +17252,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>628893</v>
+        <v>628527</v>
       </c>
       <c r="R144" t="n">
-        <v>7301743</v>
+        <v>7301837</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -17275,13 +17313,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001511</t>
+          <t>https://artportalen.se/Sighting/96001528</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>96001576</v>
+        <v>96001510</v>
       </c>
       <c r="B145" t="n">
         <v>83307</v>
@@ -17312,17 +17350,17 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>628521</v>
+        <v>628617</v>
       </c>
       <c r="R145" t="n">
-        <v>7301337</v>
+        <v>7301892</v>
       </c>
       <c r="S145" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -17366,24 +17404,24 @@
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001576</t>
+          <t>https://artportalen.se/Sighting/96001510</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>96001586</v>
+        <v>96001511</v>
       </c>
       <c r="B146" t="n">
         <v>83307</v>
@@ -17414,17 +17452,17 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>628922</v>
+        <v>628893</v>
       </c>
       <c r="R146" t="n">
-        <v>7301534</v>
+        <v>7301743</v>
       </c>
       <c r="S146" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -17468,27 +17506,27 @@
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001586</t>
+          <t>https://artportalen.se/Sighting/96001511</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>7123094</v>
+        <v>96001576</v>
       </c>
       <c r="B147" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17496,41 +17534,37 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>629036</v>
+        <v>628521</v>
       </c>
       <c r="R147" t="n">
-        <v>7301895</v>
+        <v>7301337</v>
       </c>
       <c r="S147" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T147" t="inlineStr">
         <is>
@@ -17554,17 +17588,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2012-07-23</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Sandra Laestander  ID;33448</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17579,27 +17608,27 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7123094</t>
+          <t>https://artportalen.se/Sighting/96001576</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>7123110</v>
+        <v>96001586</v>
       </c>
       <c r="B148" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17607,41 +17636,37 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Myrås, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>628905</v>
+        <v>628922</v>
       </c>
       <c r="R148" t="n">
-        <v>7301919</v>
+        <v>7301534</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T148" t="inlineStr">
         <is>
@@ -17665,17 +17690,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2012-10-01</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2012-10-01</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Lisa Lind  ID;33693</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17690,27 +17710,27 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7123110</t>
+          <t>https://artportalen.se/Sighting/96001586</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>96001512</v>
+        <v>7123094</v>
       </c>
       <c r="B149" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17718,37 +17738,41 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>628697</v>
+        <v>629036</v>
       </c>
       <c r="R149" t="n">
-        <v>7301894</v>
+        <v>7301895</v>
       </c>
       <c r="S149" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17772,12 +17796,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2012-07-23</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2012-07-23</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Sandra Laestander  ID;33448</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17792,27 +17821,27 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001512</t>
+          <t>https://artportalen.se/Sighting/7123094</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>96001513</v>
+        <v>7123110</v>
       </c>
       <c r="B150" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17820,37 +17849,41 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Myrås, Pi lm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>629004</v>
+        <v>628905</v>
       </c>
       <c r="R150" t="n">
-        <v>7301890</v>
+        <v>7301919</v>
       </c>
       <c r="S150" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17874,12 +17907,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2012-10-01</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2012-10-01</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Lisa Lind  ID;33693</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17894,24 +17932,24 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Sveaskog genom Johan Ekenstedt</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001513</t>
+          <t>https://artportalen.se/Sighting/7123110</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>96001560</v>
+        <v>96001512</v>
       </c>
       <c r="B151" t="n">
         <v>79946</v>
@@ -17942,17 +17980,17 @@
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>629048</v>
+        <v>628697</v>
       </c>
       <c r="R151" t="n">
-        <v>7301916</v>
+        <v>7301894</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17996,27 +18034,27 @@
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001560</t>
+          <t>https://artportalen.se/Sighting/96001512</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135321675</v>
+        <v>96001513</v>
       </c>
       <c r="B152" t="n">
-        <v>80060</v>
+        <v>79946</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18044,17 +18082,17 @@
       <c r="I152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>628556</v>
+        <v>629004</v>
       </c>
       <c r="R152" t="n">
-        <v>7302011</v>
+        <v>7301890</v>
       </c>
       <c r="S152" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -18078,22 +18116,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>15:47</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -18108,31 +18136,27 @@
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY152" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321675</t>
+          <t>https://artportalen.se/Sighting/96001513</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>135325385</v>
+        <v>96001560</v>
       </c>
       <c r="B153" t="n">
-        <v>80060</v>
+        <v>79946</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18160,17 +18184,17 @@
       <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>628596</v>
+        <v>629048</v>
       </c>
       <c r="R153" t="n">
-        <v>7301997</v>
+        <v>7301916</v>
       </c>
       <c r="S153" t="n">
-        <v>7</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -18194,22 +18218,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>16:03</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -18224,69 +18238,65 @@
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY153" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325385</t>
+          <t>https://artportalen.se/Sighting/96001560</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>95999775</v>
+        <v>135321675</v>
       </c>
       <c r="B154" t="n">
-        <v>80461</v>
+        <v>80060</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>628862</v>
+        <v>628556</v>
       </c>
       <c r="R154" t="n">
-        <v>7301765</v>
+        <v>7302011</v>
       </c>
       <c r="S154" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -18310,12 +18320,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18330,65 +18350,69 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Maj Aspebo, Isak Vahlström, Björn Mildh, Kristina Bäck</t>
-        </is>
-      </c>
-      <c r="AY154" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95999775</t>
+          <t>https://artportalen.se/Sighting/135321675</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>95999782</v>
+        <v>135325385</v>
       </c>
       <c r="B155" t="n">
-        <v>80467</v>
+        <v>80060</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6463</v>
+        <v>6453</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>628862</v>
+        <v>628596</v>
       </c>
       <c r="R155" t="n">
-        <v>7301765</v>
+        <v>7301997</v>
       </c>
       <c r="S155" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -18412,12 +18436,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18432,69 +18466,69 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
-        </is>
-      </c>
-      <c r="AY155" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95999782</t>
+          <t>https://artportalen.se/Sighting/135325385</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>96001509</v>
+        <v>95999775</v>
       </c>
       <c r="B156" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>628652</v>
+        <v>628862</v>
       </c>
       <c r="R156" t="n">
-        <v>7301905</v>
+        <v>7301765</v>
       </c>
       <c r="S156" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -18524,11 +18558,6 @@
       <c r="AA156" t="inlineStr">
         <is>
           <t>2021-09-09</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>hackspår</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -18548,69 +18577,60 @@
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Maj Aspebo, Isak Vahlström, Björn Mildh, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001509</t>
+          <t>https://artportalen.se/Sighting/95999775</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>96001588</v>
+        <v>95999782</v>
       </c>
       <c r="B157" t="n">
-        <v>57953</v>
+        <v>80467</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>628922</v>
+        <v>628862</v>
       </c>
       <c r="R157" t="n">
-        <v>7301534</v>
+        <v>7301765</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -18654,27 +18674,27 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001588</t>
+          <t>https://artportalen.se/Sighting/95999782</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>135326030</v>
+        <v>96001509</v>
       </c>
       <c r="B158" t="n">
-        <v>57980</v>
+        <v>57953</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18706,17 +18726,17 @@
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>628596</v>
+        <v>628652</v>
       </c>
       <c r="R158" t="n">
-        <v>7301997</v>
+        <v>7301905</v>
       </c>
       <c r="S158" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18740,34 +18760,24 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>11:04</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr">
         <is>
-          <t>Födosök</t>
+          <t>hackspår</t>
         </is>
       </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG158" t="b">
         <v>0</v>
@@ -18775,69 +18785,74 @@
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY158" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135326030</t>
+          <t>https://artportalen.se/Sighting/96001509</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>96001514</v>
+        <v>96001588</v>
       </c>
       <c r="B159" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>628527</v>
+        <v>628922</v>
       </c>
       <c r="R159" t="n">
-        <v>7301834</v>
+        <v>7301534</v>
       </c>
       <c r="S159" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18881,44 +18896,44 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001514</t>
+          <t>https://artportalen.se/Sighting/96001588</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>135321676</v>
+        <v>135326030</v>
       </c>
       <c r="B160" t="n">
-        <v>57170</v>
+        <v>57980</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -18929,25 +18944,21 @@
       <c r="I160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>628517</v>
+        <v>628596</v>
       </c>
       <c r="R160" t="n">
-        <v>7301970</v>
+        <v>7301997</v>
       </c>
       <c r="S160" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -18976,7 +18987,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18986,14 +18997,19 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Födosök</t>
         </is>
       </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG160" t="b">
         <v>0</v>
@@ -19001,12 +19017,12 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
@@ -19016,63 +19032,54 @@
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321676</t>
+          <t>https://artportalen.se/Sighting/135326030</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>96001558</v>
+        <v>96001514</v>
       </c>
       <c r="B161" t="n">
-        <v>58057</v>
+        <v>57141</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M161" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>628984</v>
+        <v>628527</v>
       </c>
       <c r="R161" t="n">
-        <v>7301812</v>
+        <v>7301834</v>
       </c>
       <c r="S161" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -19116,65 +19123,73 @@
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001558</t>
+          <t>https://artportalen.se/Sighting/96001514</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>96001517</v>
+        <v>135321676</v>
       </c>
       <c r="B162" t="n">
-        <v>56522</v>
+        <v>57170</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>206004</v>
+        <v>102613</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>628979</v>
+        <v>628517</v>
       </c>
       <c r="R162" t="n">
-        <v>7301848</v>
+        <v>7301970</v>
       </c>
       <c r="S162" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -19198,12 +19213,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -19218,27 +19243,31 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
-        </is>
-      </c>
-      <c r="AY162" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001517</t>
+          <t>https://artportalen.se/Sighting/135321676</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>96001593</v>
+        <v>96001558</v>
       </c>
       <c r="B163" t="n">
-        <v>56522</v>
+        <v>58057</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19246,26 +19275,31 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>206004</v>
+        <v>103031</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P163" t="inlineStr">
@@ -19274,10 +19308,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>628959</v>
+        <v>628984</v>
       </c>
       <c r="R163" t="n">
-        <v>7301705</v>
+        <v>7301812</v>
       </c>
       <c r="S163" t="n">
         <v>25</v>
@@ -19335,54 +19369,54 @@
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001593</t>
+          <t>https://artportalen.se/Sighting/96001558</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>96001598</v>
+        <v>96001517</v>
       </c>
       <c r="B164" t="n">
-        <v>97983</v>
+        <v>56522</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>221945</v>
+        <v>206004</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>628815</v>
+        <v>628979</v>
       </c>
       <c r="R164" t="n">
-        <v>7301412</v>
+        <v>7301848</v>
       </c>
       <c r="S164" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -19426,27 +19460,27 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001598</t>
+          <t>https://artportalen.se/Sighting/96001517</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>96001518</v>
+        <v>96001593</v>
       </c>
       <c r="B165" t="n">
-        <v>78339</v>
+        <v>56522</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19454,37 +19488,41 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>228579</v>
+        <v>206004</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P165" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>628622</v>
+        <v>628959</v>
       </c>
       <c r="R165" t="n">
-        <v>7301889</v>
+        <v>7301705</v>
       </c>
       <c r="S165" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -19528,65 +19566,65 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001518</t>
+          <t>https://artportalen.se/Sighting/96001593</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>96001519</v>
+        <v>96001598</v>
       </c>
       <c r="B166" t="n">
-        <v>78339</v>
+        <v>97983</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>228579</v>
+        <v>221945</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>brännäs, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>628799</v>
+        <v>628815</v>
       </c>
       <c r="R166" t="n">
-        <v>7301712</v>
+        <v>7301412</v>
       </c>
       <c r="S166" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19630,27 +19668,27 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Julian Klein</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001519</t>
+          <t>https://artportalen.se/Sighting/96001598</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>96001516</v>
+        <v>96001518</v>
       </c>
       <c r="B167" t="n">
-        <v>79350</v>
+        <v>78339</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19658,21 +19696,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19682,10 +19720,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>628942</v>
+        <v>628622</v>
       </c>
       <c r="R167" t="n">
-        <v>7301780</v>
+        <v>7301889</v>
       </c>
       <c r="S167" t="n">
         <v>15</v>
@@ -19743,16 +19781,16 @@
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001516</t>
+          <t>https://artportalen.se/Sighting/96001518</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>91822628</v>
+        <v>96001519</v>
       </c>
       <c r="B168" t="n">
-        <v>91909</v>
+        <v>78339</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19760,37 +19798,37 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Rutsabäcken, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>628955</v>
+        <v>628799</v>
       </c>
       <c r="R168" t="n">
-        <v>7302103</v>
+        <v>7301712</v>
       </c>
       <c r="S168" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -19814,12 +19852,12 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19834,27 +19872,27 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91822628</t>
+          <t>https://artportalen.se/Sighting/96001519</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>95999774</v>
+        <v>96001516</v>
       </c>
       <c r="B169" t="n">
-        <v>91909</v>
+        <v>79350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19862,37 +19900,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1202</v>
+        <v>260591</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>628568</v>
+        <v>628942</v>
       </c>
       <c r="R169" t="n">
-        <v>7302074</v>
+        <v>7301780</v>
       </c>
       <c r="S169" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -19941,19 +19979,19 @@
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Julian Klein, Barbara Kühn, Maj Aspebo, Isak Vahlström, Björn Mildh, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Isak Vahlström, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/95999774</t>
+          <t>https://artportalen.se/Sighting/96001516</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>96001564</v>
+        <v>91822628</v>
       </c>
       <c r="B170" t="n">
         <v>91909</v>
@@ -19984,17 +20022,17 @@
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>Rutsabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>628517</v>
+        <v>628955</v>
       </c>
       <c r="R170" t="n">
-        <v>7302135</v>
+        <v>7302103</v>
       </c>
       <c r="S170" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -20018,12 +20056,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20038,27 +20076,27 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Jonas Nordenström</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001564</t>
+          <t>https://artportalen.se/Sighting/91822628</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>96001553</v>
+        <v>95999774</v>
       </c>
       <c r="B171" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20066,21 +20104,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -20090,13 +20128,13 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>628528</v>
+        <v>628568</v>
       </c>
       <c r="R171" t="n">
-        <v>7302111</v>
+        <v>7302074</v>
       </c>
       <c r="S171" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -20140,65 +20178,65 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Julian Klein</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+          <t>Julian Klein, Barbara Kühn, Maj Aspebo, Isak Vahlström, Björn Mildh, Kristina Bäck</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001553</t>
+          <t>https://artportalen.se/Sighting/95999774</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>135321674</v>
+        <v>96001564</v>
       </c>
       <c r="B172" t="n">
-        <v>92446</v>
+        <v>91909</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4217</v>
+        <v>1202</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>628516</v>
+        <v>628517</v>
       </c>
       <c r="R172" t="n">
-        <v>7302124</v>
+        <v>7302135</v>
       </c>
       <c r="S172" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -20222,22 +20260,12 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>15:37</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20248,88 +20276,69 @@
       </c>
       <c r="AG172" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY172" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321674</t>
+          <t>https://artportalen.se/Sighting/96001564</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>135325382</v>
+        <v>96001553</v>
       </c>
       <c r="B173" t="n">
-        <v>92446</v>
+        <v>83173</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4217</v>
+        <v>1312</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>628531</v>
+        <v>628528</v>
       </c>
       <c r="R173" t="n">
-        <v>7302133</v>
+        <v>7302111</v>
       </c>
       <c r="S173" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -20353,22 +20362,12 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z173" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB173" t="inlineStr">
-        <is>
-          <t>15:38</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -20383,69 +20382,65 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY173" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325382</t>
+          <t>https://artportalen.se/Sighting/96001553</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>91822596</v>
+        <v>135321674</v>
       </c>
       <c r="B174" t="n">
-        <v>79327</v>
+        <v>92446</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Rutsabäcken, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>628919</v>
+        <v>628516</v>
       </c>
       <c r="R174" t="n">
-        <v>7302086</v>
+        <v>7302124</v>
       </c>
       <c r="S174" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -20469,12 +20464,22 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20485,69 +20490,88 @@
       </c>
       <c r="AG174" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Jonas Nordenström</t>
-        </is>
-      </c>
-      <c r="AY174" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91822596</t>
+          <t>https://artportalen.se/Sighting/135321674</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>96001562</v>
+        <v>135325382</v>
       </c>
       <c r="B175" t="n">
-        <v>78730</v>
+        <v>92446</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6437</v>
+        <v>4217</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>628494</v>
+        <v>628531</v>
       </c>
       <c r="R175" t="n">
-        <v>7302166</v>
+        <v>7302133</v>
       </c>
       <c r="S175" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="T175" t="inlineStr">
         <is>
@@ -20571,12 +20595,22 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -20591,65 +20625,69 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
-        </is>
-      </c>
-      <c r="AY175" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001562</t>
+          <t>https://artportalen.se/Sighting/135325382</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>135379346</v>
+        <v>91822596</v>
       </c>
       <c r="B176" t="n">
-        <v>78844</v>
+        <v>79327</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Rutsabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>628528</v>
+        <v>628919</v>
       </c>
       <c r="R176" t="n">
-        <v>7302157</v>
+        <v>7302086</v>
       </c>
       <c r="S176" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T176" t="inlineStr">
         <is>
@@ -20673,22 +20711,12 @@
       </c>
       <c r="Y176" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z176" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB176" t="inlineStr">
-        <is>
-          <t>15:33</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -20703,31 +20731,27 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY176" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Jonas Nordenström</t>
+        </is>
+      </c>
+      <c r="AY176" t="inlineStr"/>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135379346</t>
+          <t>https://artportalen.se/Sighting/91822596</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>96001551</v>
+        <v>96001562</v>
       </c>
       <c r="B177" t="n">
-        <v>83307</v>
+        <v>78730</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -20735,21 +20759,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -20759,10 +20783,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>628525</v>
+        <v>628494</v>
       </c>
       <c r="R177" t="n">
-        <v>7302110</v>
+        <v>7302166</v>
       </c>
       <c r="S177" t="n">
         <v>25</v>
@@ -20820,16 +20844,16 @@
       <c r="AY177" t="inlineStr"/>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001551</t>
+          <t>https://artportalen.se/Sighting/96001562</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>135321673</v>
+        <v>135379346</v>
       </c>
       <c r="B178" t="n">
-        <v>80060</v>
+        <v>78844</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20837,37 +20861,37 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
       <c r="P178" t="inlineStr">
         <is>
-          <t>lillberget, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>628582</v>
+        <v>628528</v>
       </c>
       <c r="R178" t="n">
-        <v>7302078</v>
+        <v>7302157</v>
       </c>
       <c r="S178" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T178" t="inlineStr">
         <is>
@@ -20896,7 +20920,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20906,7 +20930,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20921,12 +20945,12 @@
       <c r="AT178" t="inlineStr"/>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
@@ -20936,16 +20960,16 @@
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135321673</t>
+          <t>https://artportalen.se/Sighting/135379346</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>135379343</v>
+        <v>96001551</v>
       </c>
       <c r="B179" t="n">
-        <v>80060</v>
+        <v>83307</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20953,37 +20977,37 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
       <c r="P179" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>628556</v>
+        <v>628525</v>
       </c>
       <c r="R179" t="n">
-        <v>7302053</v>
+        <v>7302110</v>
       </c>
       <c r="S179" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="T179" t="inlineStr">
         <is>
@@ -21007,22 +21031,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>15:24</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -21037,31 +21051,27 @@
       <c r="AT179" t="inlineStr"/>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY179" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr"/>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135379343</t>
+          <t>https://artportalen.se/Sighting/96001551</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>135325381</v>
+        <v>135321673</v>
       </c>
       <c r="B180" t="n">
-        <v>57982</v>
+        <v>80060</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21069,45 +21079,37 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr"/>
       <c r="P180" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>628555</v>
+        <v>628582</v>
       </c>
       <c r="R180" t="n">
-        <v>7302119</v>
+        <v>7302078</v>
       </c>
       <c r="S180" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T180" t="inlineStr">
         <is>
@@ -21136,7 +21138,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -21146,12 +21148,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Ringhack bilder</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -21166,12 +21163,12 @@
       <c r="AT180" t="inlineStr"/>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
@@ -21181,16 +21178,16 @@
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325381</t>
+          <t>https://artportalen.se/Sighting/135321673</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>135326032</v>
+        <v>135379343</v>
       </c>
       <c r="B181" t="n">
-        <v>57980</v>
+        <v>80060</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21198,41 +21195,37 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="K181" t="inlineStr"/>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
       <c r="P181" t="inlineStr">
         <is>
           <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>628509</v>
+        <v>628556</v>
       </c>
       <c r="R181" t="n">
-        <v>7302114</v>
+        <v>7302053</v>
       </c>
       <c r="S181" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T181" t="inlineStr">
         <is>
@@ -21261,7 +21254,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -21271,19 +21264,14 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC181" t="inlineStr">
-        <is>
-          <t>Äldre födosök</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD181" t="b">
         <v>0</v>
       </c>
       <c r="AE181" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG181" t="b">
         <v>0</v>
@@ -21291,12 +21279,12 @@
       <c r="AT181" t="inlineStr"/>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
@@ -21306,63 +21294,62 @@
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135326032</t>
+          <t>https://artportalen.se/Sighting/135379343</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>96001550</v>
+        <v>135325381</v>
       </c>
       <c r="B182" t="n">
-        <v>57141</v>
+        <v>57982</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr"/>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>628527</v>
+        <v>628555</v>
       </c>
       <c r="R182" t="n">
-        <v>7302111</v>
+        <v>7302119</v>
       </c>
       <c r="S182" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -21386,12 +21373,27 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Ringhack bilder</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21406,65 +21408,73 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Anton Lundberg</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
-        </is>
-      </c>
-      <c r="AY182" t="inlineStr"/>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001550</t>
+          <t>https://artportalen.se/Sighting/135325381</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>96001565</v>
+        <v>135326032</v>
       </c>
       <c r="B183" t="n">
-        <v>92577</v>
+        <v>57980</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106596</v>
+        <v>100109</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Brännäs, Pi lm</t>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>628523</v>
+        <v>628509</v>
       </c>
       <c r="R183" t="n">
-        <v>7302128</v>
+        <v>7302114</v>
       </c>
       <c r="S183" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -21488,19 +21498,34 @@
       </c>
       <c r="Y183" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>2021-09-09</t>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Äldre födosök</t>
         </is>
       </c>
       <c r="AD183" t="b">
         <v>0</v>
       </c>
       <c r="AE183" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG183" t="b">
         <v>0</v>
@@ -21508,68 +21533,78 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Alva Dahlqvist Cederstrand</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
-        </is>
-      </c>
-      <c r="AY183" t="inlineStr"/>
+          <t>Alva Dahlqvist Cederstrand, Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96001565</t>
+          <t>https://artportalen.se/Sighting/135326032</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>135325379</v>
+        <v>96001550</v>
       </c>
       <c r="B184" t="n">
-        <v>92737</v>
+        <v>57141</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>106596</v>
+        <v>100138</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Nordlig parasitporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Antrodiella pallasii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Renvall &amp; al.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
-      <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>628509</v>
+        <v>628527</v>
       </c>
       <c r="R184" t="n">
-        <v>7302114</v>
+        <v>7302111</v>
       </c>
       <c r="S184" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -21593,105 +21628,85 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>14:59</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr">
-        <is>
-          <t>14:59</t>
-        </is>
-      </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Hittad på platsen för ett äldre fynd, men en liten inte särskilt typisk fruktkropp</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
       <c r="AE184" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF184" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY184" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135325379</t>
+          <t>https://artportalen.se/Sighting/96001550</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>135379344</v>
+        <v>96001565</v>
       </c>
       <c r="B185" t="n">
-        <v>79464</v>
+        <v>92577</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>260591</v>
+        <v>106596</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+          <t>Brännäs, Pi lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>628560</v>
+        <v>628523</v>
       </c>
       <c r="R185" t="n">
-        <v>7302107</v>
+        <v>7302128</v>
       </c>
       <c r="S185" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T185" t="inlineStr">
         <is>
@@ -21715,22 +21730,12 @@
       </c>
       <c r="Y185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2021-09-09</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -21745,69 +21750,68 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY185" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström, Julian Klein, Barbara Kühn, Björn Mildh, Maj Aspebo, Kristina Bäck</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135379344</t>
+          <t>https://artportalen.se/Sighting/96001565</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>135379345</v>
+        <v>135325379</v>
       </c>
       <c r="B186" t="n">
-        <v>79464</v>
+        <v>92737</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>260591</v>
+        <v>106596</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Nordlig parasitporing</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Antrodiella pallasii</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Renvall &amp; al.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr"/>
+      <c r="K186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>628521</v>
+        <v>628509</v>
       </c>
       <c r="R186" t="n">
-        <v>7302143</v>
+        <v>7302114</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -21836,7 +21840,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -21846,35 +21850,273 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>Hittad på platsen för ett äldre fynd, men en liten inte särskilt typisk fruktkropp</t>
         </is>
       </c>
       <c r="AD186" t="b">
         <v>0</v>
       </c>
       <c r="AE186" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135325379</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>135379344</v>
+      </c>
+      <c r="B187" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>628560</v>
+      </c>
+      <c r="R187" t="n">
+        <v>7302107</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>15:28</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AX186" t="inlineStr">
+      <c r="AX187" t="inlineStr">
         <is>
           <t>Helena Björnström</t>
         </is>
       </c>
-      <c r="AY186" t="inlineStr">
+      <c r="AY187" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
-      <c r="AZ186" t="inlineStr">
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135379344</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>135379345</v>
+      </c>
+      <c r="B188" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Siebdniesjávrrie-Lillberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>628521</v>
+      </c>
+      <c r="R188" t="n">
+        <v>7302143</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AB188" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ188" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135379345</t>
         </is>
@@ -22067,6 +22309,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83343</v>
+        <v>83347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83347</v>
+        <v>83349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83403</v>
+        <v>83404</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83403</v>
+        <v>83404</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>

--- a/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
+++ b/artfynd/Maskaure Siebdniesjávrrie-Lillberget, 122 ha artfynd.xlsx
@@ -10646,7 +10646,7 @@
         <v>137007767</v>
       </c>
       <c r="B85" t="n">
-        <v>83404</v>
+        <v>83407</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>137007768</v>
       </c>
       <c r="B86" t="n">
-        <v>83404</v>
+        <v>83407</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
